--- a/artfynd/A 48933-2025 artfynd.xlsx
+++ b/artfynd/A 48933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983123</v>
       </c>
       <c r="B2" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73983636</v>
       </c>
       <c r="B3" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74209388</v>
       </c>
       <c r="B4" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74465154</v>
       </c>
       <c r="B5" t="n">
-        <v>104116</v>
+        <v>104123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74471186</v>
       </c>
       <c r="B6" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74768634</v>
       </c>
       <c r="B7" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74844561</v>
       </c>
       <c r="B8" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48933-2025 artfynd.xlsx
+++ b/artfynd/A 48933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983123</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73983636</v>
       </c>
       <c r="B3" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74209388</v>
       </c>
       <c r="B4" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74465154</v>
       </c>
       <c r="B5" t="n">
-        <v>104126</v>
+        <v>104131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74471186</v>
       </c>
       <c r="B6" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74768634</v>
       </c>
       <c r="B7" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74844561</v>
       </c>
       <c r="B8" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48933-2025 artfynd.xlsx
+++ b/artfynd/A 48933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983123</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73983636</v>
       </c>
       <c r="B3" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74209388</v>
       </c>
       <c r="B4" t="n">
-        <v>99280</v>
+        <v>99288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74465154</v>
       </c>
       <c r="B5" t="n">
-        <v>104131</v>
+        <v>104139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74471186</v>
       </c>
       <c r="B6" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74768634</v>
       </c>
       <c r="B7" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74844561</v>
       </c>
       <c r="B8" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48933-2025 artfynd.xlsx
+++ b/artfynd/A 48933-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983123</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73983636</v>
       </c>
       <c r="B3" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74209388</v>
       </c>
       <c r="B4" t="n">
-        <v>99288</v>
+        <v>99298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74465154</v>
       </c>
       <c r="B5" t="n">
-        <v>104139</v>
+        <v>104149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74471186</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74768634</v>
       </c>
       <c r="B7" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74844561</v>
       </c>
       <c r="B8" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48933-2025 artfynd.xlsx
+++ b/artfynd/A 48933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73983123</v>
+        <v>74768634</v>
       </c>
       <c r="B2" t="n">
-        <v>107376</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Arnica montana. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Platanthera chlorantha. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73983636</v>
+        <v>73983123</v>
       </c>
       <c r="B3" t="n">
-        <v>109264</v>
+        <v>107907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Hypochoeris maculata. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Arnica montana. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74209388</v>
+        <v>74465154</v>
       </c>
       <c r="B4" t="n">
-        <v>99298</v>
+        <v>104639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222295</v>
+        <v>220164</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Carex caryophyllea. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Helianthemum nummularium. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74465154</v>
+        <v>73983636</v>
       </c>
       <c r="B5" t="n">
-        <v>104149</v>
+        <v>109814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Helianthemum nummularium. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Hypochoeris maculata. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74471186</v>
+        <v>74844561</v>
       </c>
       <c r="B6" t="n">
-        <v>100857</v>
+        <v>106155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Hepatica nobilis. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Primula veris. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74768634</v>
+        <v>74783804</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>102559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219875</v>
+        <v>222133</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Platanthera chlorantha. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Polygala vulgaris. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74844561</v>
+        <v>74209388</v>
       </c>
       <c r="B8" t="n">
-        <v>105644</v>
+        <v>99754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>222295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Primula veris. LEG: Kjell Eklund</t>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Carex caryophyllea. LEG: Kjell Eklund</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,6 +1445,117 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>74471186</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2 Boda 450 m SSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>479541</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6313325</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5E3g 0705. SOM: Hepatica nobilis. LEG: Kjell Eklund</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Sandås</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
